--- a/media/Levels/Level_11.xlsx
+++ b/media/Levels/Level_11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685BDAFD-B516-4C4B-9225-1A1D8BB9BA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676E7953-0988-4063-8C0A-972128909505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2172" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3431,19 +3431,19 @@
       <c r="EC29" s="2">
         <v>0</v>
       </c>
-      <c r="EI29" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ29" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK29" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL29" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM29" s="4">
+      <c r="EO29" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP29" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ29" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER29" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES29" s="4">
         <v>0</v>
       </c>
       <c r="ET29" s="1">
@@ -3601,19 +3601,19 @@
       <c r="EC30" s="2">
         <v>0</v>
       </c>
-      <c r="EI30" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ30" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK30" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL30" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM30" s="4">
+      <c r="EO30" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP30" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ30" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER30" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES30" s="4">
         <v>0</v>
       </c>
       <c r="ET30" s="1">
@@ -3771,19 +3771,19 @@
       <c r="EC31" s="2">
         <v>0</v>
       </c>
-      <c r="EI31" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ31" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK31" s="4">
+      <c r="EO31" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP31" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ31" s="4">
         <v>11</v>
       </c>
-      <c r="EL31" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM31" s="4">
+      <c r="ER31" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES31" s="4">
         <v>0</v>
       </c>
       <c r="ET31" s="1">
@@ -3941,19 +3941,19 @@
       <c r="EC32" s="2">
         <v>0</v>
       </c>
-      <c r="EI32" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ32" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK32" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL32" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM32" s="4">
+      <c r="EO32" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP32" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ32" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER32" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES32" s="4">
         <v>0</v>
       </c>
       <c r="ET32" s="1">
@@ -4036,19 +4036,19 @@
       <c r="EC33" s="2">
         <v>0</v>
       </c>
-      <c r="EI33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL33" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM33" s="4">
+      <c r="EO33" s="4">
+        <v>0</v>
+      </c>
+      <c r="EP33" s="4">
+        <v>0</v>
+      </c>
+      <c r="EQ33" s="4">
+        <v>0</v>
+      </c>
+      <c r="ER33" s="4">
+        <v>0</v>
+      </c>
+      <c r="ES33" s="4">
         <v>0</v>
       </c>
       <c r="ET33" s="1">
@@ -4521,21 +4521,6 @@
       <c r="CZ43" s="4">
         <v>0</v>
       </c>
-      <c r="DH43" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI43" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ43" s="4">
-        <v>0</v>
-      </c>
-      <c r="DK43" s="4">
-        <v>0</v>
-      </c>
-      <c r="DL43" s="4">
-        <v>0</v>
-      </c>
       <c r="ET43" s="1">
         <v>0</v>
       </c>
@@ -4586,21 +4571,6 @@
       <c r="CZ44" s="4">
         <v>0</v>
       </c>
-      <c r="DH44" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI44" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ44" s="4">
-        <v>0</v>
-      </c>
-      <c r="DK44" s="4">
-        <v>0</v>
-      </c>
-      <c r="DL44" s="4">
-        <v>0</v>
-      </c>
       <c r="ET44" s="1">
         <v>0</v>
       </c>
@@ -4672,31 +4642,31 @@
       <c r="Y45" s="1">
         <v>0</v>
       </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="1">
-        <v>3</v>
-      </c>
-      <c r="AH45" s="1">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>7</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>7</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>7</v>
+      </c>
+      <c r="AH45" s="3">
         <v>0</v>
       </c>
       <c r="AI45" s="1">
@@ -4882,21 +4852,6 @@
       <c r="CZ45" s="4">
         <v>0</v>
       </c>
-      <c r="DH45" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI45" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ45" s="4">
-        <v>11</v>
-      </c>
-      <c r="DK45" s="4">
-        <v>0</v>
-      </c>
-      <c r="DL45" s="4">
-        <v>0</v>
-      </c>
       <c r="ET45" s="1">
         <v>0</v>
       </c>
@@ -4944,21 +4899,6 @@
       <c r="CZ46" s="4">
         <v>0</v>
       </c>
-      <c r="DH46" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI46" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ46" s="4">
-        <v>0</v>
-      </c>
-      <c r="DK46" s="4">
-        <v>0</v>
-      </c>
-      <c r="DL46" s="4">
-        <v>0</v>
-      </c>
       <c r="ET46" s="1">
         <v>0</v>
       </c>
@@ -5006,21 +4946,6 @@
       <c r="CZ47" s="4">
         <v>0</v>
       </c>
-      <c r="DH47" s="4">
-        <v>0</v>
-      </c>
-      <c r="DI47" s="4">
-        <v>0</v>
-      </c>
-      <c r="DJ47" s="4">
-        <v>0</v>
-      </c>
-      <c r="DK47" s="4">
-        <v>0</v>
-      </c>
-      <c r="DL47" s="4">
-        <v>0</v>
-      </c>
       <c r="ET47" s="1">
         <v>0</v>
       </c>
@@ -6547,19 +6472,7 @@
       <c r="A69" s="1">
         <v>0</v>
       </c>
-      <c r="R69" s="4">
-        <v>0</v>
-      </c>
-      <c r="S69" s="4">
-        <v>0</v>
-      </c>
-      <c r="T69" s="4">
-        <v>0</v>
-      </c>
-      <c r="U69" s="4">
-        <v>0</v>
-      </c>
-      <c r="V69" s="4">
+      <c r="T69" s="1">
         <v>0</v>
       </c>
       <c r="AX69" s="1">
@@ -6636,20 +6549,8 @@
       <c r="A70" s="1">
         <v>0</v>
       </c>
-      <c r="R70" s="4">
-        <v>0</v>
-      </c>
-      <c r="S70" s="4">
-        <v>0</v>
-      </c>
-      <c r="T70" s="4">
-        <v>0</v>
-      </c>
-      <c r="U70" s="4">
-        <v>0</v>
-      </c>
-      <c r="V70" s="4">
-        <v>0</v>
+      <c r="T70" s="1">
+        <v>4</v>
       </c>
       <c r="AX70" s="1">
         <v>4</v>
@@ -6725,55 +6626,7 @@
       <c r="A71" s="1">
         <v>0</v>
       </c>
-      <c r="B71" s="1">
-        <v>0</v>
-      </c>
-      <c r="C71" s="1">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>3</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
-      <c r="I71" s="1">
-        <v>3</v>
-      </c>
-      <c r="J71" s="1">
-        <v>0</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-      <c r="L71" s="1">
-        <v>3</v>
-      </c>
-      <c r="M71" s="1">
-        <v>0</v>
-      </c>
-      <c r="R71" s="4">
-        <v>0</v>
-      </c>
-      <c r="S71" s="4">
-        <v>0</v>
-      </c>
-      <c r="T71" s="4">
-        <v>11</v>
-      </c>
-      <c r="U71" s="4">
-        <v>0</v>
-      </c>
-      <c r="V71" s="4">
+      <c r="T71" s="1">
         <v>0</v>
       </c>
       <c r="AX71" s="1">
@@ -6850,19 +6703,7 @@
       <c r="A72" s="1">
         <v>0</v>
       </c>
-      <c r="R72" s="4">
-        <v>0</v>
-      </c>
-      <c r="S72" s="4">
-        <v>0</v>
-      </c>
-      <c r="T72" s="4">
-        <v>0</v>
-      </c>
-      <c r="U72" s="4">
-        <v>0</v>
-      </c>
-      <c r="V72" s="4">
+      <c r="T72" s="1">
         <v>0</v>
       </c>
       <c r="AX72" s="1">
@@ -6939,20 +6780,8 @@
       <c r="A73" s="1">
         <v>0</v>
       </c>
-      <c r="R73" s="4">
-        <v>0</v>
-      </c>
-      <c r="S73" s="4">
-        <v>0</v>
-      </c>
-      <c r="T73" s="4">
-        <v>0</v>
-      </c>
-      <c r="U73" s="4">
-        <v>0</v>
-      </c>
-      <c r="V73" s="4">
-        <v>0</v>
+      <c r="T73" s="1">
+        <v>4</v>
       </c>
       <c r="AX73" s="1">
         <v>4</v>
@@ -7135,8 +6964,8 @@
       <c r="A75" s="1">
         <v>16</v>
       </c>
-      <c r="T75" s="1">
-        <v>4</v>
+      <c r="T75" s="3">
+        <v>0</v>
       </c>
       <c r="AX75" s="1">
         <v>0</v>
@@ -7411,24 +7240,6 @@
       <c r="EJ75" s="1">
         <v>0</v>
       </c>
-      <c r="EK75" s="1">
-        <v>0</v>
-      </c>
-      <c r="EL75" s="1">
-        <v>3</v>
-      </c>
-      <c r="EM75" s="1">
-        <v>0</v>
-      </c>
-      <c r="EN75" s="1">
-        <v>0</v>
-      </c>
-      <c r="EO75" s="1">
-        <v>3</v>
-      </c>
-      <c r="EP75" s="1">
-        <v>0</v>
-      </c>
       <c r="ET75" s="1">
         <v>16</v>
       </c>
@@ -7437,8 +7248,8 @@
       <c r="A76" s="1">
         <v>0</v>
       </c>
-      <c r="T76" s="1">
-        <v>0</v>
+      <c r="T76" s="3">
+        <v>8</v>
       </c>
       <c r="AX76" s="1">
         <v>0</v>
@@ -7521,19 +7332,10 @@
       <c r="DU76" s="4">
         <v>0</v>
       </c>
-      <c r="EE76" s="1">
-        <v>0</v>
-      </c>
-      <c r="EG76" s="3">
-        <v>0</v>
-      </c>
-      <c r="EH76" s="3">
-        <v>7</v>
-      </c>
-      <c r="EI76" s="3">
-        <v>0</v>
-      </c>
-      <c r="EK76" s="1">
+      <c r="EB76" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ76" s="1">
         <v>0</v>
       </c>
       <c r="ET76" s="1">
@@ -7628,10 +7430,10 @@
       <c r="DU77" s="4">
         <v>0</v>
       </c>
-      <c r="EE77" s="1">
+      <c r="EB77" s="1">
         <v>4</v>
       </c>
-      <c r="EK77" s="1">
+      <c r="EJ77" s="1">
         <v>4</v>
       </c>
       <c r="ET77" s="1">
@@ -7643,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX78" s="1">
         <v>0</v>
@@ -7711,10 +7513,10 @@
       <c r="CU78" s="1">
         <v>0</v>
       </c>
-      <c r="EE78" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK78" s="1">
+      <c r="EB78" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ78" s="1">
         <v>0</v>
       </c>
       <c r="ET78" s="1">
@@ -7726,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL79" s="4">
         <v>0</v>
@@ -7809,10 +7611,10 @@
       <c r="CU79" s="1">
         <v>0</v>
       </c>
-      <c r="EE79" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK79" s="1">
+      <c r="EB79" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ79" s="1">
         <v>0</v>
       </c>
       <c r="ET79" s="1">
@@ -7922,10 +7724,10 @@
       <c r="CU80" s="1">
         <v>4</v>
       </c>
-      <c r="EE80" s="1">
+      <c r="EB80" s="1">
         <v>4</v>
       </c>
-      <c r="EK80" s="1">
+      <c r="EJ80" s="1">
         <v>4</v>
       </c>
       <c r="ET80" s="1">
@@ -7936,8 +7738,35 @@
       <c r="A81" s="1">
         <v>0</v>
       </c>
+      <c r="B81" s="1">
+        <v>0</v>
+      </c>
+      <c r="C81" s="1">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>3</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0</v>
+      </c>
       <c r="T81" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="4">
         <v>0</v>
@@ -8035,10 +7864,10 @@
       <c r="CU81" s="1">
         <v>0</v>
       </c>
-      <c r="EE81" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK81" s="1">
+      <c r="EB81" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ81" s="1">
         <v>0</v>
       </c>
       <c r="ET81" s="1">
@@ -8050,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="T82" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z82" s="4">
         <v>0</v>
@@ -8148,10 +7977,10 @@
       <c r="CU82" s="1">
         <v>0</v>
       </c>
-      <c r="EE82" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK82" s="1">
+      <c r="EB82" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ82" s="1">
         <v>0</v>
       </c>
       <c r="ET82" s="1">
@@ -8261,10 +8090,10 @@
       <c r="CU83" s="1">
         <v>4</v>
       </c>
-      <c r="EE83" s="1">
+      <c r="EB83" s="1">
         <v>4</v>
       </c>
-      <c r="EK83" s="1">
+      <c r="EJ83" s="1">
         <v>4</v>
       </c>
       <c r="ET83" s="1">
@@ -8275,8 +8104,8 @@
       <c r="A84" s="1">
         <v>0</v>
       </c>
-      <c r="T84" s="3">
-        <v>8</v>
+      <c r="T84" s="1">
+        <v>0</v>
       </c>
       <c r="Z84" s="4">
         <v>0</v>
@@ -8359,10 +8188,10 @@
       <c r="CU84" s="1">
         <v>0</v>
       </c>
-      <c r="EE84" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK84" s="1">
+      <c r="EB84" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ84" s="1">
         <v>0</v>
       </c>
       <c r="ET84" s="1">
@@ -8373,8 +8202,8 @@
       <c r="A85" s="1">
         <v>0</v>
       </c>
-      <c r="T85" s="3">
-        <v>0</v>
+      <c r="T85" s="1">
+        <v>4</v>
       </c>
       <c r="AX85" s="1">
         <v>0</v>
@@ -8442,19 +8271,7 @@
       <c r="CU85" s="1">
         <v>0</v>
       </c>
-      <c r="EI85" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ85" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK85" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL85" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM85" s="4">
+      <c r="EJ85" s="1">
         <v>0</v>
       </c>
       <c r="ET85" s="1">
@@ -8474,20 +8291,8 @@
       <c r="CU86" s="1">
         <v>4</v>
       </c>
-      <c r="EI86" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ86" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK86" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL86" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM86" s="4">
-        <v>0</v>
+      <c r="EJ86" s="1">
+        <v>4</v>
       </c>
       <c r="ET86" s="1">
         <v>0</v>
@@ -8498,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX87" s="1">
         <v>0</v>
@@ -8506,19 +8311,7 @@
       <c r="CU87" s="1">
         <v>0</v>
       </c>
-      <c r="EI87" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ87" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK87" s="4">
-        <v>11</v>
-      </c>
-      <c r="EL87" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM87" s="4">
+      <c r="EJ87" s="1">
         <v>0</v>
       </c>
       <c r="ET87" s="1">
@@ -8530,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV88" s="4">
         <v>0</v>
@@ -8562,19 +8355,7 @@
       <c r="CW88" s="4">
         <v>0</v>
       </c>
-      <c r="EI88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL88" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM88" s="4">
+      <c r="EJ88" s="1">
         <v>0</v>
       </c>
       <c r="ET88" s="1">
@@ -8585,19 +8366,7 @@
       <c r="A89" s="1">
         <v>0</v>
       </c>
-      <c r="R89" s="4">
-        <v>0</v>
-      </c>
-      <c r="S89" s="4">
-        <v>0</v>
-      </c>
-      <c r="T89" s="4">
-        <v>0</v>
-      </c>
-      <c r="U89" s="4">
-        <v>0</v>
-      </c>
-      <c r="V89" s="4">
+      <c r="T89" s="1">
         <v>0</v>
       </c>
       <c r="AV89" s="4">
@@ -8630,20 +8399,8 @@
       <c r="CW89" s="4">
         <v>0</v>
       </c>
-      <c r="EI89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EJ89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EK89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EL89" s="4">
-        <v>0</v>
-      </c>
-      <c r="EM89" s="4">
-        <v>0</v>
+      <c r="EJ89" s="1">
+        <v>4</v>
       </c>
       <c r="ET89" s="1">
         <v>0</v>
@@ -8653,19 +8410,7 @@
       <c r="A90" s="1">
         <v>0</v>
       </c>
-      <c r="R90" s="4">
-        <v>0</v>
-      </c>
-      <c r="S90" s="4">
-        <v>0</v>
-      </c>
-      <c r="T90" s="4">
-        <v>0</v>
-      </c>
-      <c r="U90" s="4">
-        <v>0</v>
-      </c>
-      <c r="V90" s="4">
+      <c r="T90" s="1">
         <v>0</v>
       </c>
       <c r="AV90" s="4">
@@ -8698,10 +8443,7 @@
       <c r="CW90" s="4">
         <v>0</v>
       </c>
-      <c r="EE90" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK90" s="1">
+      <c r="EJ90" s="1">
         <v>0</v>
       </c>
       <c r="ET90" s="1">
@@ -8712,20 +8454,8 @@
       <c r="A91" s="1">
         <v>0</v>
       </c>
-      <c r="R91" s="4">
-        <v>0</v>
-      </c>
-      <c r="S91" s="4">
-        <v>0</v>
-      </c>
-      <c r="T91" s="4">
-        <v>11</v>
-      </c>
-      <c r="U91" s="4">
-        <v>0</v>
-      </c>
-      <c r="V91" s="4">
-        <v>0</v>
+      <c r="T91" s="1">
+        <v>4</v>
       </c>
       <c r="AV91" s="4">
         <v>0</v>
@@ -8757,11 +8487,8 @@
       <c r="CW91" s="4">
         <v>0</v>
       </c>
-      <c r="EE91" s="1">
-        <v>4</v>
-      </c>
-      <c r="EK91" s="1">
-        <v>4</v>
+      <c r="EJ91" s="1">
+        <v>0</v>
       </c>
       <c r="ET91" s="1">
         <v>0</v>
@@ -8771,19 +8498,7 @@
       <c r="A92" s="1">
         <v>0</v>
       </c>
-      <c r="R92" s="4">
-        <v>0</v>
-      </c>
-      <c r="S92" s="4">
-        <v>0</v>
-      </c>
-      <c r="T92" s="4">
-        <v>0</v>
-      </c>
-      <c r="U92" s="4">
-        <v>0</v>
-      </c>
-      <c r="V92" s="4">
+      <c r="T92" s="1">
         <v>0</v>
       </c>
       <c r="AV92" s="4">
@@ -8816,11 +8531,8 @@
       <c r="CW92" s="4">
         <v>0</v>
       </c>
-      <c r="EE92" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK92" s="1">
-        <v>0</v>
+      <c r="EJ92" s="1">
+        <v>4</v>
       </c>
       <c r="ET92" s="1">
         <v>0</v>
@@ -8830,19 +8542,7 @@
       <c r="A93" s="1">
         <v>0</v>
       </c>
-      <c r="R93" s="4">
-        <v>0</v>
-      </c>
-      <c r="S93" s="4">
-        <v>0</v>
-      </c>
-      <c r="T93" s="4">
-        <v>0</v>
-      </c>
-      <c r="U93" s="4">
-        <v>0</v>
-      </c>
-      <c r="V93" s="4">
+      <c r="T93" s="1">
         <v>0</v>
       </c>
       <c r="AX93" s="1">
@@ -8851,10 +8551,10 @@
       <c r="CU93" s="1">
         <v>0</v>
       </c>
-      <c r="EE93" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK93" s="1">
+      <c r="EB93" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ93" s="1">
         <v>0</v>
       </c>
       <c r="ET93" s="1">
@@ -8866,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX94" s="1">
         <v>4</v>
@@ -8874,11 +8574,11 @@
       <c r="CU94" s="1">
         <v>4</v>
       </c>
-      <c r="EE94" s="1">
+      <c r="EB94" s="1">
         <v>4</v>
       </c>
-      <c r="EK94" s="1">
-        <v>4</v>
+      <c r="EJ94" s="1">
+        <v>0</v>
       </c>
       <c r="ET94" s="1">
         <v>0</v>
@@ -8943,19 +8643,19 @@
         <v>0</v>
       </c>
       <c r="T95" s="1">
+        <v>0</v>
+      </c>
+      <c r="AX95" s="1">
+        <v>0</v>
+      </c>
+      <c r="CU95" s="1">
+        <v>0</v>
+      </c>
+      <c r="EB95" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ95" s="1">
         <v>4</v>
-      </c>
-      <c r="AX95" s="1">
-        <v>0</v>
-      </c>
-      <c r="CU95" s="1">
-        <v>0</v>
-      </c>
-      <c r="EE95" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK95" s="1">
-        <v>0</v>
       </c>
       <c r="ET95" s="1">
         <v>0</v>
@@ -8974,10 +8674,10 @@
       <c r="CU96" s="1">
         <v>0</v>
       </c>
-      <c r="EE96" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK96" s="1">
+      <c r="EB96" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ96" s="1">
         <v>0</v>
       </c>
       <c r="ET96" s="1">
@@ -8988,20 +8688,8 @@
       <c r="A97" s="1">
         <v>0</v>
       </c>
-      <c r="R97" s="4">
-        <v>0</v>
-      </c>
-      <c r="S97" s="4">
-        <v>0</v>
-      </c>
-      <c r="T97" s="4">
-        <v>0</v>
-      </c>
-      <c r="U97" s="4">
-        <v>0</v>
-      </c>
-      <c r="V97" s="4">
-        <v>0</v>
+      <c r="T97" s="1">
+        <v>4</v>
       </c>
       <c r="AX97" s="1">
         <v>4</v>
@@ -9009,11 +8697,11 @@
       <c r="CU97" s="1">
         <v>4</v>
       </c>
-      <c r="EE97" s="1">
+      <c r="EB97" s="1">
         <v>4</v>
       </c>
-      <c r="EK97" s="1">
-        <v>4</v>
+      <c r="EJ97" s="1">
+        <v>0</v>
       </c>
       <c r="ET97" s="1">
         <v>0</v>
@@ -9023,19 +8711,7 @@
       <c r="A98" s="1">
         <v>0</v>
       </c>
-      <c r="R98" s="4">
-        <v>0</v>
-      </c>
-      <c r="S98" s="4">
-        <v>0</v>
-      </c>
-      <c r="T98" s="4">
-        <v>0</v>
-      </c>
-      <c r="U98" s="4">
-        <v>0</v>
-      </c>
-      <c r="V98" s="4">
+      <c r="T98" s="1">
         <v>0</v>
       </c>
       <c r="AX98" s="1">
@@ -9044,11 +8720,11 @@
       <c r="CU98" s="1">
         <v>0</v>
       </c>
-      <c r="EE98" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK98" s="1">
-        <v>0</v>
+      <c r="EB98" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ98" s="1">
+        <v>4</v>
       </c>
       <c r="ET98" s="1">
         <v>0</v>
@@ -9058,19 +8734,7 @@
       <c r="A99" s="1">
         <v>0</v>
       </c>
-      <c r="R99" s="4">
-        <v>0</v>
-      </c>
-      <c r="S99" s="4">
-        <v>0</v>
-      </c>
-      <c r="T99" s="4">
-        <v>11</v>
-      </c>
-      <c r="U99" s="4">
-        <v>0</v>
-      </c>
-      <c r="V99" s="4">
+      <c r="T99" s="1">
         <v>0</v>
       </c>
       <c r="AX99" s="1">
@@ -9079,10 +8743,10 @@
       <c r="CU99" s="1">
         <v>0</v>
       </c>
-      <c r="EE99" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK99" s="1">
+      <c r="EB99" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ99" s="1">
         <v>0</v>
       </c>
       <c r="ET99" s="1">
@@ -9093,20 +8757,8 @@
       <c r="A100" s="1">
         <v>0</v>
       </c>
-      <c r="R100" s="4">
-        <v>0</v>
-      </c>
-      <c r="S100" s="4">
-        <v>0</v>
-      </c>
-      <c r="T100" s="4">
-        <v>0</v>
-      </c>
-      <c r="U100" s="4">
-        <v>0</v>
-      </c>
-      <c r="V100" s="4">
-        <v>0</v>
+      <c r="T100" s="1">
+        <v>4</v>
       </c>
       <c r="AX100" s="1">
         <v>4</v>
@@ -9114,11 +8766,11 @@
       <c r="CU100" s="1">
         <v>4</v>
       </c>
-      <c r="EE100" s="1">
+      <c r="EB100" s="1">
         <v>4</v>
       </c>
-      <c r="EK100" s="1">
-        <v>4</v>
+      <c r="EJ100" s="1">
+        <v>0</v>
       </c>
       <c r="ET100" s="1">
         <v>0</v>
@@ -9128,19 +8780,7 @@
       <c r="A101" s="1">
         <v>0</v>
       </c>
-      <c r="R101" s="4">
-        <v>0</v>
-      </c>
-      <c r="S101" s="4">
-        <v>0</v>
-      </c>
-      <c r="T101" s="4">
-        <v>0</v>
-      </c>
-      <c r="U101" s="4">
-        <v>0</v>
-      </c>
-      <c r="V101" s="4">
+      <c r="T101" s="1">
         <v>0</v>
       </c>
       <c r="AX101" s="1">
@@ -9149,11 +8789,11 @@
       <c r="CU101" s="1">
         <v>0</v>
       </c>
-      <c r="EE101" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK101" s="1">
-        <v>0</v>
+      <c r="EB101" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ101" s="1">
+        <v>4</v>
       </c>
       <c r="ET101" s="1">
         <v>0</v>
@@ -9172,10 +8812,10 @@
       <c r="CU102" s="1">
         <v>0</v>
       </c>
-      <c r="EE102" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK102" s="3">
+      <c r="EB102" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ102" s="1">
         <v>0</v>
       </c>
       <c r="ET102" s="1">
@@ -9225,11 +8865,11 @@
       <c r="CU103" s="1">
         <v>4</v>
       </c>
-      <c r="EE103" s="1">
+      <c r="EB103" s="1">
         <v>4</v>
       </c>
-      <c r="EK103" s="3">
-        <v>8</v>
+      <c r="EJ103" s="1">
+        <v>0</v>
       </c>
       <c r="ET103" s="1">
         <v>0</v>
@@ -9278,11 +8918,11 @@
       <c r="CU104" s="1">
         <v>0</v>
       </c>
-      <c r="EE104" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK104" s="3">
-        <v>0</v>
+      <c r="EB104" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ104" s="1">
+        <v>4</v>
       </c>
       <c r="ET104" s="1">
         <v>0</v>
@@ -9601,58 +9241,52 @@
       <c r="DV105" s="1">
         <v>0</v>
       </c>
-      <c r="DW105" s="1">
-        <v>0</v>
-      </c>
-      <c r="DX105" s="1">
+      <c r="DW105" s="3">
+        <v>0</v>
+      </c>
+      <c r="DX105" s="3">
+        <v>7</v>
+      </c>
+      <c r="DY105" s="3">
+        <v>0</v>
+      </c>
+      <c r="DZ105" s="1">
+        <v>0</v>
+      </c>
+      <c r="EA105" s="1">
         <v>3</v>
       </c>
-      <c r="DY105" s="1">
-        <v>0</v>
-      </c>
-      <c r="DZ105" s="3">
-        <v>0</v>
-      </c>
-      <c r="EA105" s="3">
+      <c r="EB105" s="1">
+        <v>0</v>
+      </c>
+      <c r="EJ105" s="1">
+        <v>0</v>
+      </c>
+      <c r="EK105" s="3">
+        <v>0</v>
+      </c>
+      <c r="EL105" s="3">
         <v>7</v>
       </c>
-      <c r="EB105" s="3">
-        <v>0</v>
-      </c>
-      <c r="EC105" s="1">
-        <v>0</v>
-      </c>
-      <c r="ED105" s="1">
-        <v>3</v>
-      </c>
-      <c r="EE105" s="1">
-        <v>0</v>
-      </c>
-      <c r="EK105" s="1">
-        <v>0</v>
-      </c>
-      <c r="EL105" s="1">
-        <v>3</v>
-      </c>
-      <c r="EM105" s="1">
-        <v>0</v>
-      </c>
-      <c r="EN105" s="1">
-        <v>0</v>
-      </c>
-      <c r="EO105" s="1">
-        <v>3</v>
-      </c>
-      <c r="EP105" s="1">
-        <v>0</v>
-      </c>
-      <c r="EQ105" s="1">
-        <v>0</v>
-      </c>
-      <c r="ER105" s="1">
-        <v>3</v>
-      </c>
-      <c r="ES105" s="1">
+      <c r="EM105" s="3">
+        <v>0</v>
+      </c>
+      <c r="EN105" s="3">
+        <v>0</v>
+      </c>
+      <c r="EO105" s="3">
+        <v>7</v>
+      </c>
+      <c r="EP105" s="3">
+        <v>0</v>
+      </c>
+      <c r="EQ105" s="3">
+        <v>0</v>
+      </c>
+      <c r="ER105" s="3">
+        <v>7</v>
+      </c>
+      <c r="ES105" s="3">
         <v>0</v>
       </c>
       <c r="ET105" s="1">
@@ -9702,7 +9336,7 @@
       <c r="CD106" s="1">
         <v>0</v>
       </c>
-      <c r="EE106" s="1">
+      <c r="EB106" s="1">
         <v>0</v>
       </c>
       <c r="ET106" s="1">
@@ -9752,7 +9386,7 @@
       <c r="CD107" s="1">
         <v>4</v>
       </c>
-      <c r="EE107" s="1">
+      <c r="EB107" s="1">
         <v>4</v>
       </c>
       <c r="ET107" s="1">
@@ -9787,7 +9421,7 @@
       <c r="CD108" s="1">
         <v>0</v>
       </c>
-      <c r="EE108" s="1">
+      <c r="EB108" s="1">
         <v>0</v>
       </c>
       <c r="ET108" s="1">
@@ -9816,13 +9450,13 @@
       <c r="BF109" s="4">
         <v>0</v>
       </c>
-      <c r="BO109" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD109" s="1">
-        <v>0</v>
-      </c>
-      <c r="EE109" s="1">
+      <c r="BO109" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD109" s="3">
+        <v>0</v>
+      </c>
+      <c r="EB109" s="1">
         <v>0</v>
       </c>
       <c r="ET109" s="1">
@@ -9851,13 +9485,13 @@
       <c r="BF110" s="4">
         <v>0</v>
       </c>
-      <c r="BO110" s="1">
-        <v>4</v>
-      </c>
-      <c r="CD110" s="1">
-        <v>4</v>
-      </c>
-      <c r="EE110" s="1">
+      <c r="BO110" s="3">
+        <v>8</v>
+      </c>
+      <c r="CD110" s="3">
+        <v>8</v>
+      </c>
+      <c r="EB110" s="1">
         <v>4</v>
       </c>
       <c r="ET110" s="1">
@@ -9886,13 +9520,13 @@
       <c r="BF111" s="4">
         <v>0</v>
       </c>
-      <c r="BO111" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD111" s="1">
-        <v>0</v>
-      </c>
-      <c r="EE111" s="1">
+      <c r="BO111" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD111" s="3">
+        <v>0</v>
+      </c>
+      <c r="EB111" s="1">
         <v>0</v>
       </c>
       <c r="ET111" s="1">
@@ -9927,7 +9561,7 @@
       <c r="CD112" s="3">
         <v>0</v>
       </c>
-      <c r="EE112" s="1">
+      <c r="EB112" s="1">
         <v>0</v>
       </c>
       <c r="ET112" s="1">
@@ -9947,7 +9581,7 @@
       <c r="CD113" s="3">
         <v>8</v>
       </c>
-      <c r="EE113" s="1">
+      <c r="EB113" s="1">
         <v>4</v>
       </c>
       <c r="ET113" s="1">
@@ -9967,7 +9601,7 @@
       <c r="CD114" s="3">
         <v>0</v>
       </c>
-      <c r="EE114" s="1">
+      <c r="EB114" s="1">
         <v>0</v>
       </c>
       <c r="ET114" s="1">
@@ -9987,7 +9621,7 @@
       <c r="CD115" s="3">
         <v>0</v>
       </c>
-      <c r="EE115" s="1">
+      <c r="EB115" s="1">
         <v>0</v>
       </c>
       <c r="ET115" s="1">
@@ -10007,7 +9641,7 @@
       <c r="CD116" s="3">
         <v>8</v>
       </c>
-      <c r="EE116" s="1">
+      <c r="EB116" s="1">
         <v>4</v>
       </c>
       <c r="ET116" s="1">
@@ -10042,7 +9676,7 @@
       <c r="CD117" s="3">
         <v>0</v>
       </c>
-      <c r="EE117" s="1">
+      <c r="EB117" s="1">
         <v>0</v>
       </c>
       <c r="ET117" s="1">
@@ -10056,12 +9690,6 @@
       <c r="T118" s="1">
         <v>0</v>
       </c>
-      <c r="Y118" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z118" s="2">
-        <v>0</v>
-      </c>
       <c r="AA118" s="2">
         <v>0</v>
       </c>
@@ -10116,6 +9744,12 @@
       <c r="AR118" s="2">
         <v>0</v>
       </c>
+      <c r="AS118" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT118" s="2">
+        <v>0</v>
+      </c>
       <c r="BB118" s="4">
         <v>0</v>
       </c>
@@ -10137,6 +9771,9 @@
       <c r="CD118" s="1">
         <v>0</v>
       </c>
+      <c r="CO118" s="2">
+        <v>0</v>
+      </c>
       <c r="CP118" s="2">
         <v>0</v>
       </c>
@@ -10194,7 +9831,7 @@
       <c r="DH118" s="2">
         <v>0</v>
       </c>
-      <c r="DI118" s="2">
+      <c r="DS118" s="2">
         <v>0</v>
       </c>
       <c r="DT118" s="2">
@@ -10252,9 +9889,6 @@
         <v>0</v>
       </c>
       <c r="EL118" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM118" s="2">
         <v>0</v>
       </c>
       <c r="ET118" s="1">
@@ -10268,12 +9902,6 @@
       <c r="T119" s="1">
         <v>4</v>
       </c>
-      <c r="Y119" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="2">
-        <v>0</v>
-      </c>
       <c r="AA119" s="2">
         <v>0</v>
       </c>
@@ -10326,6 +9954,12 @@
         <v>0</v>
       </c>
       <c r="AR119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS119" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT119" s="2">
         <v>0</v>
       </c>
       <c r="BB119" s="4">
@@ -10349,6 +9983,9 @@
       <c r="CD119" s="1">
         <v>4</v>
       </c>
+      <c r="CO119" s="2">
+        <v>0</v>
+      </c>
       <c r="CP119" s="2">
         <v>0</v>
       </c>
@@ -10406,7 +10043,7 @@
       <c r="DH119" s="2">
         <v>0</v>
       </c>
-      <c r="DI119" s="2">
+      <c r="DS119" s="2">
         <v>0</v>
       </c>
       <c r="DT119" s="2">
@@ -10464,9 +10101,6 @@
         <v>0</v>
       </c>
       <c r="EL119" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM119" s="2">
         <v>0</v>
       </c>
       <c r="ET119" s="1">
@@ -10480,12 +10114,6 @@
       <c r="T120" s="1">
         <v>0</v>
       </c>
-      <c r="Y120" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z120" s="2">
-        <v>0</v>
-      </c>
       <c r="AA120" s="2">
         <v>0</v>
       </c>
@@ -10540,6 +10168,12 @@
       <c r="AR120" s="2">
         <v>0</v>
       </c>
+      <c r="AS120" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT120" s="2">
+        <v>0</v>
+      </c>
       <c r="BB120" s="4">
         <v>0</v>
       </c>
@@ -10561,6 +10195,9 @@
       <c r="CD120" s="1">
         <v>0</v>
       </c>
+      <c r="CO120" s="2">
+        <v>0</v>
+      </c>
       <c r="CP120" s="2">
         <v>0</v>
       </c>
@@ -10618,7 +10255,7 @@
       <c r="DH120" s="2">
         <v>0</v>
       </c>
-      <c r="DI120" s="2">
+      <c r="DS120" s="2">
         <v>0</v>
       </c>
       <c r="DT120" s="2">
@@ -10676,9 +10313,6 @@
         <v>0</v>
       </c>
       <c r="EL120" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM120" s="2">
         <v>0</v>
       </c>
       <c r="ET120" s="1">
@@ -10692,12 +10326,6 @@
       <c r="T121" s="1">
         <v>0</v>
       </c>
-      <c r="Y121" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z121" s="2">
-        <v>0</v>
-      </c>
       <c r="AA121" s="2">
         <v>0</v>
       </c>
@@ -10752,6 +10380,12 @@
       <c r="AR121" s="2">
         <v>0</v>
       </c>
+      <c r="AS121" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT121" s="2">
+        <v>0</v>
+      </c>
       <c r="BB121" s="4">
         <v>0</v>
       </c>
@@ -10773,6 +10407,9 @@
       <c r="CD121" s="1">
         <v>0</v>
       </c>
+      <c r="CO121" s="2">
+        <v>0</v>
+      </c>
       <c r="CP121" s="2">
         <v>0</v>
       </c>
@@ -10830,7 +10467,7 @@
       <c r="DH121" s="2">
         <v>0</v>
       </c>
-      <c r="DI121" s="2">
+      <c r="DS121" s="2">
         <v>0</v>
       </c>
       <c r="DT121" s="2">
@@ -10888,9 +10525,6 @@
         <v>0</v>
       </c>
       <c r="EL121" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM121" s="2">
         <v>0</v>
       </c>
       <c r="ET121" s="1">
@@ -10904,12 +10538,6 @@
       <c r="T122" s="1">
         <v>4</v>
       </c>
-      <c r="Y122" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z122" s="2">
-        <v>0</v>
-      </c>
       <c r="AA122" s="2">
         <v>0</v>
       </c>
@@ -10962,6 +10590,12 @@
         <v>0</v>
       </c>
       <c r="AR122" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS122" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT122" s="2">
         <v>0</v>
       </c>
       <c r="BO122" s="1">
@@ -10970,6 +10604,9 @@
       <c r="CD122" s="1">
         <v>4</v>
       </c>
+      <c r="CO122" s="2">
+        <v>0</v>
+      </c>
       <c r="CP122" s="2">
         <v>0</v>
       </c>
@@ -11027,7 +10664,7 @@
       <c r="DH122" s="2">
         <v>0</v>
       </c>
-      <c r="DI122" s="2">
+      <c r="DS122" s="2">
         <v>0</v>
       </c>
       <c r="DT122" s="2">
@@ -11085,9 +10722,6 @@
         <v>0</v>
       </c>
       <c r="EL122" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM122" s="2">
         <v>0</v>
       </c>
       <c r="ET122" s="1">
@@ -11101,12 +10735,6 @@
       <c r="T123" s="1">
         <v>0</v>
       </c>
-      <c r="Y123" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z123" s="2">
-        <v>0</v>
-      </c>
       <c r="AA123" s="2">
         <v>0</v>
       </c>
@@ -11161,12 +10789,21 @@
       <c r="AR123" s="2">
         <v>0</v>
       </c>
+      <c r="AS123" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT123" s="2">
+        <v>0</v>
+      </c>
       <c r="BO123" s="1">
         <v>0</v>
       </c>
       <c r="CD123" s="1">
         <v>0</v>
       </c>
+      <c r="CO123" s="2">
+        <v>0</v>
+      </c>
       <c r="CP123" s="2">
         <v>0</v>
       </c>
@@ -11224,7 +10861,7 @@
       <c r="DH123" s="2">
         <v>0</v>
       </c>
-      <c r="DI123" s="2">
+      <c r="DS123" s="2">
         <v>0</v>
       </c>
       <c r="DT123" s="2">
@@ -11282,9 +10919,6 @@
         <v>0</v>
       </c>
       <c r="EL123" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM123" s="2">
         <v>0</v>
       </c>
       <c r="ET123" s="1">
@@ -11295,25 +10929,7 @@
       <c r="A124" s="1">
         <v>0</v>
       </c>
-      <c r="R124" s="4">
-        <v>0</v>
-      </c>
-      <c r="S124" s="4">
-        <v>0</v>
-      </c>
-      <c r="T124" s="4">
-        <v>0</v>
-      </c>
-      <c r="U124" s="4">
-        <v>0</v>
-      </c>
-      <c r="V124" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y124" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z124" s="2">
+      <c r="T124" s="1">
         <v>0</v>
       </c>
       <c r="AA124" s="2">
@@ -11370,6 +10986,12 @@
       <c r="AR124" s="2">
         <v>0</v>
       </c>
+      <c r="AS124" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT124" s="2">
+        <v>0</v>
+      </c>
       <c r="BB124" s="4">
         <v>0</v>
       </c>
@@ -11391,6 +11013,9 @@
       <c r="CD124" s="1">
         <v>0</v>
       </c>
+      <c r="CO124" s="2">
+        <v>0</v>
+      </c>
       <c r="CP124" s="2">
         <v>0</v>
       </c>
@@ -11448,7 +11073,7 @@
       <c r="DH124" s="2">
         <v>0</v>
       </c>
-      <c r="DI124" s="2">
+      <c r="DS124" s="2">
         <v>0</v>
       </c>
       <c r="DT124" s="2">
@@ -11506,9 +11131,6 @@
         <v>0</v>
       </c>
       <c r="EL124" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM124" s="2">
         <v>0</v>
       </c>
       <c r="ET124" s="1">
@@ -11519,26 +11141,8 @@
       <c r="A125" s="1">
         <v>0</v>
       </c>
-      <c r="R125" s="4">
-        <v>0</v>
-      </c>
-      <c r="S125" s="4">
-        <v>0</v>
-      </c>
-      <c r="T125" s="4">
-        <v>0</v>
-      </c>
-      <c r="U125" s="4">
-        <v>0</v>
-      </c>
-      <c r="V125" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y125" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z125" s="2">
-        <v>0</v>
+      <c r="T125" s="1">
+        <v>4</v>
       </c>
       <c r="AA125" s="2">
         <v>0</v>
@@ -11592,6 +11196,12 @@
         <v>0</v>
       </c>
       <c r="AR125" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS125" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT125" s="2">
         <v>0</v>
       </c>
       <c r="BB125" s="4">
@@ -11615,6 +11225,9 @@
       <c r="CD125" s="1">
         <v>4</v>
       </c>
+      <c r="CO125" s="2">
+        <v>0</v>
+      </c>
       <c r="CP125" s="2">
         <v>0</v>
       </c>
@@ -11672,7 +11285,7 @@
       <c r="DH125" s="2">
         <v>0</v>
       </c>
-      <c r="DI125" s="2">
+      <c r="DS125" s="2">
         <v>0</v>
       </c>
       <c r="DT125" s="2">
@@ -11730,9 +11343,6 @@
         <v>0</v>
       </c>
       <c r="EL125" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM125" s="2">
         <v>0</v>
       </c>
       <c r="ET125" s="1">
@@ -11743,25 +11353,7 @@
       <c r="A126" s="1">
         <v>0</v>
       </c>
-      <c r="R126" s="4">
-        <v>0</v>
-      </c>
-      <c r="S126" s="4">
-        <v>0</v>
-      </c>
-      <c r="T126" s="4">
-        <v>11</v>
-      </c>
-      <c r="U126" s="4">
-        <v>0</v>
-      </c>
-      <c r="V126" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y126" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z126" s="2">
+      <c r="T126" s="1">
         <v>0</v>
       </c>
       <c r="AA126" s="2">
@@ -11816,6 +11408,12 @@
         <v>0</v>
       </c>
       <c r="AR126" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS126" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT126" s="2">
         <v>0</v>
       </c>
       <c r="BB126" s="4">
@@ -11839,6 +11437,9 @@
       <c r="CD126" s="1">
         <v>0</v>
       </c>
+      <c r="CO126" s="2">
+        <v>0</v>
+      </c>
       <c r="CP126" s="2">
         <v>0</v>
       </c>
@@ -11896,7 +11497,7 @@
       <c r="DH126" s="2">
         <v>0</v>
       </c>
-      <c r="DI126" s="2">
+      <c r="DS126" s="2">
         <v>0</v>
       </c>
       <c r="DT126" s="2">
@@ -11954,9 +11555,6 @@
         <v>0</v>
       </c>
       <c r="EL126" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM126" s="2">
         <v>0</v>
       </c>
       <c r="ET126" s="1">
@@ -11967,25 +11565,7 @@
       <c r="A127" s="1">
         <v>0</v>
       </c>
-      <c r="R127" s="4">
-        <v>0</v>
-      </c>
-      <c r="S127" s="4">
-        <v>0</v>
-      </c>
-      <c r="T127" s="4">
-        <v>0</v>
-      </c>
-      <c r="U127" s="4">
-        <v>0</v>
-      </c>
-      <c r="V127" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y127" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z127" s="2">
+      <c r="T127" s="1">
         <v>0</v>
       </c>
       <c r="AA127" s="2">
@@ -12013,14 +11593,14 @@
         <v>0</v>
       </c>
       <c r="AI127" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ127" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK127" s="2">
         <v>12</v>
       </c>
-      <c r="AJ127" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK127" s="2">
-        <v>0</v>
-      </c>
       <c r="AL127" s="2">
         <v>0</v>
       </c>
@@ -12042,6 +11622,12 @@
       <c r="AR127" s="2">
         <v>0</v>
       </c>
+      <c r="AS127" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT127" s="2">
+        <v>0</v>
+      </c>
       <c r="BB127" s="4">
         <v>0</v>
       </c>
@@ -12063,6 +11649,9 @@
       <c r="CD127" s="1">
         <v>0</v>
       </c>
+      <c r="CO127" s="2">
+        <v>0</v>
+      </c>
       <c r="CP127" s="2">
         <v>0</v>
       </c>
@@ -12091,70 +11680,70 @@
         <v>0</v>
       </c>
       <c r="CY127" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CZ127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DS127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DT127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DU127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DV127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DW127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DX127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DY127" s="2">
+        <v>0</v>
+      </c>
+      <c r="DZ127" s="2">
+        <v>0</v>
+      </c>
+      <c r="EA127" s="2">
+        <v>0</v>
+      </c>
+      <c r="EB127" s="2">
+        <v>0</v>
+      </c>
+      <c r="EC127" s="2">
         <v>12</v>
       </c>
-      <c r="DA127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DT127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DU127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DV127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DW127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DX127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DY127" s="2">
-        <v>0</v>
-      </c>
-      <c r="DZ127" s="2">
-        <v>0</v>
-      </c>
-      <c r="EA127" s="2">
-        <v>0</v>
-      </c>
-      <c r="EB127" s="2">
-        <v>0</v>
-      </c>
-      <c r="EC127" s="2">
-        <v>0</v>
-      </c>
       <c r="ED127" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="EE127" s="2">
         <v>0</v>
@@ -12178,9 +11767,6 @@
         <v>0</v>
       </c>
       <c r="EL127" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM127" s="2">
         <v>0</v>
       </c>
       <c r="ET127" s="1">
@@ -12191,26 +11777,8 @@
       <c r="A128" s="1">
         <v>0</v>
       </c>
-      <c r="R128" s="4">
-        <v>0</v>
-      </c>
-      <c r="S128" s="4">
-        <v>0</v>
-      </c>
-      <c r="T128" s="4">
-        <v>0</v>
-      </c>
-      <c r="U128" s="4">
-        <v>0</v>
-      </c>
-      <c r="V128" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y128" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z128" s="2">
-        <v>0</v>
+      <c r="T128" s="1">
+        <v>4</v>
       </c>
       <c r="AA128" s="2">
         <v>0</v>
@@ -12264,6 +11832,12 @@
         <v>0</v>
       </c>
       <c r="AR128" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS128" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT128" s="2">
         <v>0</v>
       </c>
       <c r="BB128" s="4">
@@ -12287,6 +11861,9 @@
       <c r="CD128" s="1">
         <v>4</v>
       </c>
+      <c r="CO128" s="2">
+        <v>0</v>
+      </c>
       <c r="CP128" s="2">
         <v>0</v>
       </c>
@@ -12344,7 +11921,7 @@
       <c r="DH128" s="2">
         <v>0</v>
       </c>
-      <c r="DI128" s="2">
+      <c r="DS128" s="2">
         <v>0</v>
       </c>
       <c r="DT128" s="2">
@@ -12402,9 +11979,6 @@
         <v>0</v>
       </c>
       <c r="EL128" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM128" s="2">
         <v>0</v>
       </c>
       <c r="ET128" s="1">
@@ -12418,12 +11992,6 @@
       <c r="T129" s="1">
         <v>0</v>
       </c>
-      <c r="Y129" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="2">
-        <v>0</v>
-      </c>
       <c r="AA129" s="2">
         <v>0</v>
       </c>
@@ -12478,12 +12046,21 @@
       <c r="AR129" s="2">
         <v>0</v>
       </c>
+      <c r="AS129" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT129" s="2">
+        <v>0</v>
+      </c>
       <c r="BO129" s="1">
         <v>0</v>
       </c>
       <c r="CD129" s="1">
         <v>0</v>
       </c>
+      <c r="CO129" s="2">
+        <v>0</v>
+      </c>
       <c r="CP129" s="2">
         <v>0</v>
       </c>
@@ -12541,7 +12118,7 @@
       <c r="DH129" s="2">
         <v>0</v>
       </c>
-      <c r="DI129" s="2">
+      <c r="DS129" s="2">
         <v>0</v>
       </c>
       <c r="DT129" s="2">
@@ -12599,9 +12176,6 @@
         <v>0</v>
       </c>
       <c r="EL129" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM129" s="2">
         <v>0</v>
       </c>
       <c r="ET129" s="1">
@@ -12613,12 +12187,6 @@
         <v>0</v>
       </c>
       <c r="T130" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y130" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z130" s="2">
         <v>0</v>
       </c>
       <c r="AA130" s="2">
@@ -12675,10 +12243,67 @@
       <c r="AR130" s="2">
         <v>0</v>
       </c>
+      <c r="AS130" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT130" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN130" s="1">
+        <v>0</v>
+      </c>
       <c r="BO130" s="1">
+        <v>3</v>
+      </c>
+      <c r="BP130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR130" s="1">
+        <v>3</v>
+      </c>
+      <c r="BS130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU130" s="1">
+        <v>3</v>
+      </c>
+      <c r="BV130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX130" s="1">
+        <v>3</v>
+      </c>
+      <c r="BY130" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ130" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA130" s="1">
+        <v>3</v>
+      </c>
+      <c r="CB130" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC130" s="1">
         <v>0</v>
       </c>
       <c r="CD130" s="1">
+        <v>3</v>
+      </c>
+      <c r="CE130" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO130" s="2">
         <v>0</v>
       </c>
       <c r="CP130" s="2">
@@ -12738,7 +12363,7 @@
       <c r="DH130" s="2">
         <v>0</v>
       </c>
-      <c r="DI130" s="2">
+      <c r="DS130" s="2">
         <v>0</v>
       </c>
       <c r="DT130" s="2">
@@ -12796,9 +12421,6 @@
         <v>0</v>
       </c>
       <c r="EL130" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM130" s="2">
         <v>0</v>
       </c>
       <c r="ET130" s="1">
@@ -12810,13 +12432,7 @@
         <v>0</v>
       </c>
       <c r="T131" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y131" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA131" s="2">
         <v>0</v>
@@ -12872,6 +12488,12 @@
       <c r="AR131" s="2">
         <v>0</v>
       </c>
+      <c r="AS131" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT131" s="2">
+        <v>0</v>
+      </c>
       <c r="BB131" s="4">
         <v>0</v>
       </c>
@@ -12887,29 +12509,8 @@
       <c r="BF131" s="4">
         <v>0</v>
       </c>
-      <c r="BO131" s="1">
-        <v>4</v>
-      </c>
-      <c r="BT131" s="3">
-        <v>0</v>
-      </c>
-      <c r="BU131" s="3">
-        <v>7</v>
-      </c>
-      <c r="BV131" s="3">
-        <v>0</v>
-      </c>
-      <c r="BW131" s="3">
-        <v>0</v>
-      </c>
-      <c r="BX131" s="3">
-        <v>7</v>
-      </c>
-      <c r="BY131" s="3">
-        <v>0</v>
-      </c>
-      <c r="CD131" s="1">
-        <v>4</v>
+      <c r="CO131" s="2">
+        <v>0</v>
       </c>
       <c r="CP131" s="2">
         <v>0</v>
@@ -12968,7 +12569,7 @@
       <c r="DH131" s="2">
         <v>0</v>
       </c>
-      <c r="DI131" s="2">
+      <c r="DS131" s="2">
         <v>0</v>
       </c>
       <c r="DT131" s="2">
@@ -13026,9 +12627,6 @@
         <v>0</v>
       </c>
       <c r="EL131" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM131" s="2">
         <v>0</v>
       </c>
       <c r="ET131" s="1">
@@ -13042,12 +12640,6 @@
       <c r="T132" s="1">
         <v>0</v>
       </c>
-      <c r="Y132" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="2">
-        <v>0</v>
-      </c>
       <c r="AA132" s="2">
         <v>0</v>
       </c>
@@ -13102,6 +12694,12 @@
       <c r="AR132" s="2">
         <v>0</v>
       </c>
+      <c r="AS132" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT132" s="2">
+        <v>0</v>
+      </c>
       <c r="BB132" s="4">
         <v>0</v>
       </c>
@@ -13117,52 +12715,7 @@
       <c r="BF132" s="4">
         <v>0</v>
       </c>
-      <c r="BO132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ132" s="1">
-        <v>3</v>
-      </c>
-      <c r="BR132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT132" s="1">
-        <v>3</v>
-      </c>
-      <c r="BU132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY132" s="1">
-        <v>3</v>
-      </c>
-      <c r="BZ132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB132" s="1">
-        <v>3</v>
-      </c>
-      <c r="CC132" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD132" s="1">
+      <c r="CO132" s="2">
         <v>0</v>
       </c>
       <c r="CP132" s="2">
@@ -13222,7 +12775,7 @@
       <c r="DH132" s="2">
         <v>0</v>
       </c>
-      <c r="DI132" s="2">
+      <c r="DS132" s="2">
         <v>0</v>
       </c>
       <c r="DT132" s="2">
@@ -13280,9 +12833,6 @@
         <v>0</v>
       </c>
       <c r="EL132" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM132" s="2">
         <v>0</v>
       </c>
       <c r="ET132" s="1">
@@ -13294,12 +12844,6 @@
         <v>0</v>
       </c>
       <c r="T133" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y133" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="2">
         <v>0</v>
       </c>
       <c r="AA133" s="2">
@@ -13354,6 +12898,12 @@
         <v>0</v>
       </c>
       <c r="AR133" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS133" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT133" s="2">
         <v>0</v>
       </c>
       <c r="BB133" s="4">
@@ -13371,11 +12921,8 @@
       <c r="BF133" s="4">
         <v>0</v>
       </c>
-      <c r="BV133" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW133" s="1">
-        <v>4</v>
+      <c r="CO133" s="2">
+        <v>0</v>
       </c>
       <c r="CP133" s="2">
         <v>0</v>
@@ -13434,7 +12981,7 @@
       <c r="DH133" s="2">
         <v>0</v>
       </c>
-      <c r="DI133" s="2">
+      <c r="DS133" s="2">
         <v>0</v>
       </c>
       <c r="DT133" s="2">
@@ -13492,9 +13039,6 @@
         <v>0</v>
       </c>
       <c r="EL133" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM133" s="2">
         <v>0</v>
       </c>
       <c r="ET133" s="1">
@@ -13506,13 +13050,7 @@
         <v>0</v>
       </c>
       <c r="T134" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y134" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA134" s="2">
         <v>0</v>
@@ -13568,6 +13106,12 @@
       <c r="AR134" s="2">
         <v>0</v>
       </c>
+      <c r="AS134" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT134" s="2">
+        <v>0</v>
+      </c>
       <c r="BB134" s="4">
         <v>0</v>
       </c>
@@ -13583,10 +13127,7 @@
       <c r="BF134" s="4">
         <v>0</v>
       </c>
-      <c r="BV134" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW134" s="1">
+      <c r="CO134" s="2">
         <v>0</v>
       </c>
       <c r="CP134" s="2">
@@ -13646,7 +13187,7 @@
       <c r="DH134" s="2">
         <v>0</v>
       </c>
-      <c r="DI134" s="2">
+      <c r="DS134" s="2">
         <v>0</v>
       </c>
       <c r="DT134" s="2">
@@ -13704,9 +13245,6 @@
         <v>0</v>
       </c>
       <c r="EL134" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM134" s="2">
         <v>0</v>
       </c>
       <c r="ET134" s="1">
@@ -13720,12 +13258,6 @@
       <c r="T135" s="1">
         <v>0</v>
       </c>
-      <c r="Y135" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="2">
-        <v>0</v>
-      </c>
       <c r="AA135" s="2">
         <v>0</v>
       </c>
@@ -13780,6 +13312,12 @@
       <c r="AR135" s="2">
         <v>0</v>
       </c>
+      <c r="AS135" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT135" s="2">
+        <v>0</v>
+      </c>
       <c r="BB135" s="4">
         <v>0</v>
       </c>
@@ -13795,10 +13333,7 @@
       <c r="BF135" s="4">
         <v>0</v>
       </c>
-      <c r="BV135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW135" s="1">
+      <c r="CO135" s="2">
         <v>0</v>
       </c>
       <c r="CP135" s="2">
@@ -13858,7 +13393,7 @@
       <c r="DH135" s="2">
         <v>0</v>
       </c>
-      <c r="DI135" s="2">
+      <c r="DS135" s="2">
         <v>0</v>
       </c>
       <c r="DT135" s="2">
@@ -13916,9 +13451,6 @@
         <v>0</v>
       </c>
       <c r="EL135" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM135" s="2">
         <v>0</v>
       </c>
       <c r="ET135" s="1">
@@ -13930,12 +13462,6 @@
         <v>0</v>
       </c>
       <c r="T136" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y136" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="2">
         <v>0</v>
       </c>
       <c r="AA136" s="2">
@@ -13992,11 +13518,14 @@
       <c r="AR136" s="2">
         <v>0</v>
       </c>
-      <c r="BV136" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW136" s="1">
-        <v>4</v>
+      <c r="AS136" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT136" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO136" s="2">
+        <v>0</v>
       </c>
       <c r="CP136" s="2">
         <v>0</v>
@@ -14055,7 +13584,7 @@
       <c r="DH136" s="2">
         <v>0</v>
       </c>
-      <c r="DI136" s="2">
+      <c r="DS136" s="2">
         <v>0</v>
       </c>
       <c r="DT136" s="2">
@@ -14113,9 +13642,6 @@
         <v>0</v>
       </c>
       <c r="EL136" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM136" s="2">
         <v>0</v>
       </c>
       <c r="ET136" s="1">
@@ -14127,13 +13653,7 @@
         <v>0</v>
       </c>
       <c r="T137" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA137" s="2">
         <v>0</v>
@@ -14189,10 +13709,13 @@
       <c r="AR137" s="2">
         <v>0</v>
       </c>
-      <c r="BV137" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW137" s="1">
+      <c r="AS137" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT137" s="2">
+        <v>0</v>
+      </c>
+      <c r="CO137" s="2">
         <v>0</v>
       </c>
       <c r="CP137" s="2">
@@ -14252,7 +13775,7 @@
       <c r="DH137" s="2">
         <v>0</v>
       </c>
-      <c r="DI137" s="2">
+      <c r="DS137" s="2">
         <v>0</v>
       </c>
       <c r="DT137" s="2">
@@ -14310,9 +13833,6 @@
         <v>0</v>
       </c>
       <c r="EL137" s="2">
-        <v>0</v>
-      </c>
-      <c r="EM137" s="2">
         <v>0</v>
       </c>
       <c r="ET137" s="1">
@@ -14341,13 +13861,7 @@
       <c r="BF138" s="4">
         <v>0</v>
       </c>
-      <c r="BV138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW138" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ138" s="1">
+      <c r="CX138" s="1">
         <v>0</v>
       </c>
       <c r="ET138" s="1">
@@ -14358,9 +13872,6 @@
       <c r="A139" s="1">
         <v>0</v>
       </c>
-      <c r="T139" s="1">
-        <v>4</v>
-      </c>
       <c r="BB139" s="4">
         <v>0</v>
       </c>
@@ -14376,13 +13887,7 @@
       <c r="BF139" s="4">
         <v>0</v>
       </c>
-      <c r="BV139" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW139" s="1">
-        <v>4</v>
-      </c>
-      <c r="CZ139" s="1">
+      <c r="CX139" s="1">
         <v>4</v>
       </c>
       <c r="ET139" s="1">
@@ -14393,9 +13898,6 @@
       <c r="A140" s="1">
         <v>0</v>
       </c>
-      <c r="T140" s="1">
-        <v>0</v>
-      </c>
       <c r="BB140" s="4">
         <v>0</v>
       </c>
@@ -14411,13 +13913,7 @@
       <c r="BF140" s="4">
         <v>0</v>
       </c>
-      <c r="BV140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW140" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ140" s="1">
+      <c r="CX140" s="1">
         <v>0</v>
       </c>
       <c r="ET140" s="1">
@@ -14428,9 +13924,6 @@
       <c r="A141" s="1">
         <v>0</v>
       </c>
-      <c r="T141" s="1">
-        <v>0</v>
-      </c>
       <c r="BB141" s="4">
         <v>0</v>
       </c>
@@ -14446,13 +13939,7 @@
       <c r="BF141" s="4">
         <v>0</v>
       </c>
-      <c r="BV141" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW141" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ141" s="1">
+      <c r="CX141" s="1">
         <v>0</v>
       </c>
       <c r="ET141" s="1">
@@ -14463,9 +13950,6 @@
       <c r="A142" s="1">
         <v>0</v>
       </c>
-      <c r="T142" s="1">
-        <v>4</v>
-      </c>
       <c r="BB142" s="4">
         <v>0</v>
       </c>
@@ -14481,13 +13965,7 @@
       <c r="BF142" s="4">
         <v>0</v>
       </c>
-      <c r="BV142" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW142" s="1">
-        <v>4</v>
-      </c>
-      <c r="CZ142" s="1">
+      <c r="CX142" s="1">
         <v>4</v>
       </c>
       <c r="ET142" s="1">
@@ -14498,16 +13976,7 @@
       <c r="A143" s="1">
         <v>0</v>
       </c>
-      <c r="T143" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV143" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW143" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ143" s="1">
+      <c r="CX143" s="1">
         <v>0</v>
       </c>
       <c r="ET143" s="1">
@@ -14518,16 +13987,7 @@
       <c r="A144" s="1">
         <v>0</v>
       </c>
-      <c r="T144" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV144" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW144" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ144" s="1">
+      <c r="CX144" s="1">
         <v>0</v>
       </c>
       <c r="ET144" s="1">
@@ -14538,9 +13998,6 @@
       <c r="A145" s="1">
         <v>0</v>
       </c>
-      <c r="T145" s="1">
-        <v>4</v>
-      </c>
       <c r="BB145" s="4">
         <v>0</v>
       </c>
@@ -14556,13 +14013,7 @@
       <c r="BF145" s="4">
         <v>0</v>
       </c>
-      <c r="BV145" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW145" s="1">
-        <v>4</v>
-      </c>
-      <c r="CZ145" s="1">
+      <c r="CX145" s="1">
         <v>4</v>
       </c>
       <c r="ET145" s="1">
@@ -14573,9 +14024,6 @@
       <c r="B146" s="1">
         <v>4</v>
       </c>
-      <c r="T146" s="1">
-        <v>0</v>
-      </c>
       <c r="BB146" s="4">
         <v>0</v>
       </c>
@@ -14591,13 +14039,7 @@
       <c r="BF146" s="4">
         <v>0</v>
       </c>
-      <c r="BV146" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW146" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ146" s="1">
+      <c r="CX146" s="1">
         <v>0</v>
       </c>
       <c r="ES146" s="1">
@@ -14608,9 +14050,6 @@
       <c r="C147" s="1">
         <v>0</v>
       </c>
-      <c r="T147" s="1">
-        <v>0</v>
-      </c>
       <c r="BB147" s="4">
         <v>0</v>
       </c>
@@ -14626,13 +14065,7 @@
       <c r="BF147" s="4">
         <v>0</v>
       </c>
-      <c r="BV147" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW147" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ147" s="1">
+      <c r="CX147" s="1">
         <v>0</v>
       </c>
       <c r="ER147" s="1">
@@ -14643,9 +14076,6 @@
       <c r="D148" s="1">
         <v>0</v>
       </c>
-      <c r="T148" s="1">
-        <v>4</v>
-      </c>
       <c r="BB148" s="4">
         <v>0</v>
       </c>
@@ -14661,13 +14091,7 @@
       <c r="BF148" s="4">
         <v>0</v>
       </c>
-      <c r="BV148" s="1">
-        <v>4</v>
-      </c>
-      <c r="BW148" s="1">
-        <v>4</v>
-      </c>
-      <c r="CZ148" s="1">
+      <c r="CX148" s="1">
         <v>4</v>
       </c>
       <c r="EQ148" s="1">
@@ -14678,9 +14102,6 @@
       <c r="E149" s="1">
         <v>4</v>
       </c>
-      <c r="T149" s="1">
-        <v>0</v>
-      </c>
       <c r="BB149" s="4">
         <v>0</v>
       </c>
@@ -14696,13 +14117,7 @@
       <c r="BF149" s="4">
         <v>0</v>
       </c>
-      <c r="BV149" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW149" s="1">
-        <v>0</v>
-      </c>
-      <c r="CZ149" s="1">
+      <c r="CX149" s="1">
         <v>0</v>
       </c>
       <c r="EP149" s="1">

--- a/media/Levels/Level_11.xlsx
+++ b/media/Levels/Level_11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685BDAFD-B516-4C4B-9225-1A1D8BB9BA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FC334F-EB8E-4BFF-B77D-589C2F81D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2172" yWindow="72" windowWidth="13836" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="BX1" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="75" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="T75" s="1">
         <v>4</v>
@@ -7430,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="ET75" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:150" x14ac:dyDescent="0.45">
@@ -14921,7 +14921,7 @@
         <v>0</v>
       </c>
       <c r="BX150" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>

--- a/media/Levels/Level_11.xlsx
+++ b/media/Levels/Level_11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676E7953-0988-4063-8C0A-972128909505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E1B834-04AE-4022-A69F-6B0BE5694F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV9" s="1">
         <v>4</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV10" s="1">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV12" s="1">
         <v>4</v>
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="2">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="2">
         <v>0</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="2">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI18" s="2">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="2">
         <v>0</v>
@@ -1978,20 +1978,8 @@
       <c r="A21" s="1">
         <v>0</v>
       </c>
-      <c r="V21" s="4">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4">
-        <v>0</v>
-      </c>
-      <c r="X21" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>0</v>
+      <c r="X21" s="1">
+        <v>4</v>
       </c>
       <c r="AI21" s="2">
         <v>0</v>
@@ -2355,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="4">
         <v>0</v>
@@ -2522,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y24" s="4">
         <v>0</v>
@@ -2849,7 +2837,19 @@
       <c r="A26" s="1">
         <v>0</v>
       </c>
-      <c r="X26" s="1">
+      <c r="V26" s="4">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4">
+        <v>0</v>
+      </c>
+      <c r="X26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="4">
         <v>0</v>
       </c>
       <c r="AI26" s="2">
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="2">
         <v>0</v>
@@ -3130,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI28" s="2">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="2">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI31" s="2">
         <v>0</v>

--- a/media/Levels/Level_11.xlsx
+++ b/media/Levels/Level_11.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E1B834-04AE-4022-A69F-6B0BE5694F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222B5C04-3E6F-45A7-9E16-29144C9B4F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -667,10 +667,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX1" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -14333,10 +14333,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX150" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>
